--- a/02_shoe_photo/shoe_photo_metadata.xlsx
+++ b/02_shoe_photo/shoe_photo_metadata.xlsx
@@ -337,7 +337,7 @@
     </x:row>
     <x:row r="2" ht="90" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>IMG_012684.png</x:v>
+        <x:v>IMG_012684.jpg</x:v>
       </x:c>
       <x:c r="B2" s="12" t="n">
         <x:v>46293.597291666665</x:v>
@@ -363,7 +363,7 @@
     </x:row>
     <x:row r="3" ht="90" customHeight="1">
       <x:c r="A3" s="11" t="str">
-        <x:v>IMG_004318.png</x:v>
+        <x:v>IMG_004318.jpg</x:v>
       </x:c>
       <x:c r="B3" s="12" t="n">
         <x:v>45018.44604166667</x:v>
@@ -389,7 +389,7 @@
     </x:row>
     <x:row r="4" ht="90" customHeight="1">
       <x:c r="A4" s="11" t="str">
-        <x:v>IMG_006825.png</x:v>
+        <x:v>IMG_006825.jpg</x:v>
       </x:c>
       <x:c r="B4" s="12" t="n">
         <x:v>45451.64355324074</x:v>
@@ -415,7 +415,7 @@
     </x:row>
     <x:row r="5" ht="90" customHeight="1">
       <x:c r="A5" s="11" t="str">
-        <x:v>IMG_007986.png</x:v>
+        <x:v>IMG_007986.jpg</x:v>
       </x:c>
       <x:c r="B5" s="12" t="n">
         <x:v>45556.76356481481</x:v>
@@ -441,7 +441,7 @@
     </x:row>
     <x:row r="6" ht="90" customHeight="1">
       <x:c r="A6" s="11" t="str">
-        <x:v>IMG_009641.png</x:v>
+        <x:v>IMG_009641.jpg</x:v>
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:v>45766.575104166666</x:v>
@@ -467,7 +467,7 @@
     </x:row>
     <x:row r="7" ht="90" customHeight="1">
       <x:c r="A7" s="11" t="str">
-        <x:v>IMG_011872.png</x:v>
+        <x:v>IMG_011872.jpg</x:v>
       </x:c>
       <x:c r="B7" s="12" t="n">
         <x:v>46254.36309027778</x:v>
